--- a/docs/validation/V01_Staged_vs_Loaded_Rows.xlsx
+++ b/docs/validation/V01_Staged_vs_Loaded_Rows.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="29" customHeight="1">
+    <row r="60" ht="43" customHeight="1">
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>The load leaves a staged row out for one of three reasons. This query counts each. Run it the same way — select the old text in the query window, delete it, paste this, press F5.</t>
+          <t>The load leaves a staged row out for one of five reasons — the three checks in its WHERE and date join, plus a supplier or item that has no row in its dimension table. This query counts each. Every column name is prefixed with src. so that a column of the same name in DimDate cannot be picked up by mistake. Run it the same way — select the old text in the query window, delete it, paste this, press F5.</t>
         </is>
       </c>
     </row>
@@ -1280,21 +1280,21 @@
     <row r="62" ht="15" customHeight="1">
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, [YEAR]) IS NULL</t>
+          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, src.[YEAR]) IS NULL</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">              OR TRY_CONVERT(int, [MONTH]) IS NULL</t>
+          <t xml:space="preserve">              OR TRY_CONVERT(int, src.[MONTH]) IS NULL</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">              OR TRY_CONVERT(int, [MONTH]) NOT BETWEEN 1 AND 12</t>
+          <t xml:space="preserve">              OR TRY_CONVERT(int, src.[MONTH]) NOT BETWEEN 1 AND 12</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SUM(CASE WHEN NULLIF(LTRIM(RTRIM([ITEM CODE])), '') IS NULL</t>
+          <t xml:space="preserve">    SUM(CASE WHEN NULLIF(LTRIM(RTRIM(src.[ITEM CODE])), '') IS NULL</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, [MONTH]) BETWEEN 1 AND 12</t>
+          <t xml:space="preserve">    SUM(CASE WHEN TRY_CONVERT(int, src.[MONTH]) BETWEEN 1 AND 12</t>
         </is>
       </c>
     </row>
@@ -1336,281 +1336,261 @@
     <row r="70" ht="15" customHeight="1">
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">                              WHERE d.DateKey = TRY_CONVERT(int, [YEAR])  * 10000</t>
+          <t xml:space="preserve">                              WHERE d.DateKey = TRY_CONVERT(int, src.[YEAR])  * 10000</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                              + TRY_CONVERT(int, [MONTH]) * 100 + 1)</t>
+          <t xml:space="preserve">                                              + TRY_CONVERT(int, src.[MONTH]) * 100 + 1)</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">             THEN 1 ELSE 0 END)                         AS DateOutsideDimDate</t>
+          <t xml:space="preserve">             THEN 1 ELSE 0 END)                         AS DateOutsideDimDate,</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>FROM stg.WarehouseRetailSales;</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="6" customHeight="1"/>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="16" t="n">
+          <t xml:space="preserve">    SUM(CASE WHEN NOT EXISTS (SELECT 1 FROM dw.DimSupplier AS s</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              WHERE s.SupplierName = COALESCE(</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                    NULLIF(LTRIM(RTRIM(src.[SUPPLIER])), ''), 'Unknown Supplier'))</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             THEN 1 ELSE 0 END)                         AS SupplierNotInDimSupplier,</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SUM(CASE WHEN NULLIF(LTRIM(RTRIM(src.[ITEM CODE])), '') IS NOT NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              AND NOT EXISTS (SELECT 1 FROM dw.DimItem AS i</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              WHERE i.ItemCode = LTRIM(RTRIM(src.[ITEM CODE])))</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             THEN 1 ELSE 0 END)                         AS ItemNotInDimItem</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>FROM stg.WarehouseRetailSales AS src;</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>Write down the three numbers: BadYearOrMonth, BlankItemCode and DateOutsideDimDate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="29" customHeight="1">
-      <c r="A76" s="16" t="n">
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Write down the five numbers: BadYearOrMonth, BlankItemCode, DateOutsideDimDate, SupplierNotInDimSupplier and ItemNotInDimItem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="29.5" customHeight="1">
+      <c r="A84" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>One row can be counted under more than one reason, so the three can add up to more than the difference. What matters is whether every dropped row falls under at least one of them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="8" customHeight="1"/>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>One row can be counted under more than one reason, so the five can add up to more than the difference. What matters is whether every dropped row falls under at least one of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="8" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="B79" s="14" t="inlineStr">
+    <row r="87" ht="16" customHeight="1">
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="B80" s="6" t="inlineStr">
+    <row r="88" ht="20" customHeight="1">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>If you see</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>It means</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="D88" s="8" t="n"/>
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="B81" s="10" t="inlineStr">
+      <c r="F88" s="8" t="n"/>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>StagedRows and LoadedRows are equal</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>Nothing was lost</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="56" customHeight="1">
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>LoadedRows is smaller, and the three reasons account for every missing row</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="F89" s="8" t="n"/>
+    </row>
+    <row r="90" ht="56" customHeight="1">
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>LoadedRows is smaller, and the five reasons account for every missing row</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
         <is>
           <t>Rows were left out for a known, legitimate reason — a row with no item code cannot belong to an item</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="12" t="inlineStr">
         <is>
           <t>Pass — write the reason down</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="56" customHeight="1">
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>LoadedRows is smaller, and some missing rows fit none of the three reasons</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="F90" s="8" t="n"/>
+    </row>
+    <row r="91" ht="56" customHeight="1">
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>LoadedRows is smaller, and some missing rows fit none of the five reasons</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
         <is>
           <t>Rows were lost for a reason nobody understands</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="B84" s="12" t="inlineStr">
+      <c r="F91" s="8" t="n"/>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>LoadedRows is larger than StagedRows</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C92" s="12" t="inlineStr">
         <is>
           <t>The fact table was loaded twice, or something besides the load wrote to it</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="D92" s="8" t="n"/>
+      <c r="E92" s="12" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="B85" s="18" t="inlineStr">
+      <c r="F92" s="8" t="n"/>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="B93" s="18" t="inlineStr">
         <is>
           <t>Remember.  The criterion allows a gap only if it is explained. ‘Close enough’ is not a result: 3 missing rows out of 330,080 are 3 records nobody can account for.</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="8" customHeight="1"/>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="94" ht="8" customHeight="1"/>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="B88" s="13" t="inlineStr">
+    <row r="96" ht="20" customHeight="1">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>6.1 In document 22</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B90" s="14" t="inlineStr">
-        <is>
-          <t>Select the Run Summary tab. Find the row for this run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="29" customHeight="1">
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="29" customHeight="1">
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C92" s="14" t="inlineStr">
-        <is>
-          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="29" customHeight="1">
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="inlineStr">
-        <is>
-          <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="B95" s="19" t="inlineStr">
-        <is>
-          <t>git -C X:\retail-sector-health log -1 --format=%h</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="6" customHeight="1"/>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 1.</t>
+          <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Fill in four cells on that row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
+          <t>Select the Run Summary tab. Find the row for this run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="29" customHeight="1">
       <c r="B99" s="17" t="inlineStr">
         <is>
           <t>◦</t>
@@ -1618,11 +1598,11 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
+          <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="29" customHeight="1">
       <c r="B100" s="17" t="inlineStr">
         <is>
           <t>◦</t>
@@ -1630,11 +1610,11 @@
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
+          <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="29" customHeight="1">
       <c r="B101" s="17" t="inlineStr">
         <is>
           <t>◦</t>
@@ -1642,7 +1622,7 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>Checked by: your name or initials.</t>
+          <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
         </is>
       </c>
     </row>
@@ -1654,123 +1634,105 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
+          <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>git -C X:\retail-sector-health log -1 --format=%h</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="6" customHeight="1"/>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>Fill in four cells on that row:</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="B108" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>Checked by: your name or initials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
           <t>Date checked: today’s date.</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="16" t="n">
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B103" s="14" t="inlineStr">
+      <c r="B111" s="14" t="inlineStr">
         <is>
           <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="B104" s="6" t="inlineStr">
+    <row r="112" ht="20" customHeight="1">
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>Situation</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>Write this in Observed value / evidence</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="8" t="n"/>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>Example of a pass</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>Staged 330,080 · Loaded 330,080 · difference 0</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="n"/>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>Example of another result</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>Staged 330,080 · Loaded 330,068 · 12 dropped — all 12 have a blank ITEM CODE (diagnostic query, V01 step)</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="n"/>
-      <c r="E106" s="7" t="n"/>
-      <c r="F106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="B107" s="20" t="inlineStr">
-        <is>
-          <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="B108" s="13" t="inlineStr">
-        <is>
-          <t>6.2 In document 26</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B109" s="14" t="inlineStr">
-        <is>
-          <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="29" customHeight="1">
-      <c r="A110" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B110" s="14" t="inlineStr">
-        <is>
-          <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>Ref in doc 26</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>When it applies</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>G1.05</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>First build, right after sql/05</t>
         </is>
       </c>
       <c r="D112" s="7" t="n"/>
@@ -1778,503 +1740,626 @@
       <c r="F112" s="8" t="n"/>
     </row>
     <row r="113" ht="16" customHeight="1">
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>G5.01</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>The model pass, before publishing the model</t>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Example of a pass</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Staged 330,080 · Loaded 330,080 · difference 0</t>
         </is>
       </c>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
       <c r="F113" s="8" t="n"/>
     </row>
-    <row r="114" ht="8" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>7. IF IT FAILS</t>
+    <row r="114" ht="28" customHeight="1">
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>Example of another result</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Staged 330,080 · Loaded 330,068 · 12 dropped — all 12 have a blank ITEM CODE (diagnostic query, V01 step)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="n"/>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="8" t="n"/>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="B115" s="20" t="inlineStr">
+        <is>
+          <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="B116" s="13" t="inlineStr">
         <is>
+          <t>6.2 In document 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="29" customHeight="1">
+      <c r="A118" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Ref in doc 26</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>When it applies</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="8" t="n"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>G1.05</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>First build, right after sql/05</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="8" t="n"/>
+    </row>
+    <row r="121" ht="16" customHeight="1">
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>G5.01</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>The model pass, before publishing the model</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="8" t="n"/>
+    </row>
+    <row r="122" ht="8" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>7. IF IT FAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="B124" s="13" t="inlineStr">
+        <is>
           <t>7.1 What usually causes it</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="B117" s="6" t="inlineStr">
+    <row r="125" ht="20" customHeight="1">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>What you see</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>Likely cause</t>
         </is>
       </c>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>What to do</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n"/>
-    </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="B118" s="10" t="inlineStr">
+      <c r="F125" s="8" t="n"/>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>LoadedRows is 0</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>Script 05 created the table but the load procedure did not run, or ran before the dimensions were filled</t>
         </is>
       </c>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="10" t="inlineStr">
         <is>
           <t>Run sql/04, then sql/05 again</t>
         </is>
       </c>
-      <c r="F118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="42" customHeight="1">
-      <c r="B119" s="12" t="inlineStr">
+      <c r="F126" s="8" t="n"/>
+    </row>
+    <row r="127" ht="42" customHeight="1">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>BadYearOrMonth is not 0</t>
         </is>
       </c>
-      <c r="C119" s="12" t="inlineStr">
+      <c r="C127" s="12" t="inlineStr">
         <is>
           <t>The CSV has text or blanks in YEAR or MONTH</t>
         </is>
       </c>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="12" t="inlineStr">
+      <c r="D127" s="8" t="n"/>
+      <c r="E127" s="12" t="inlineStr">
         <is>
           <t>Look at those rows in the staging table; fix the cleansing in sql/04 or document them as unusable</t>
         </is>
       </c>
-      <c r="F119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="28" customHeight="1">
-      <c r="B120" s="10" t="inlineStr">
+      <c r="F127" s="8" t="n"/>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="B128" s="10" t="inlineStr">
         <is>
           <t>DateOutsideDimDate is not 0</t>
         </is>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C128" s="10" t="inlineStr">
         <is>
           <t>The data has a month before January 2015 or after December 2030</t>
         </is>
       </c>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="10" t="inlineStr">
         <is>
           <t>Extend the date range in sql/04, re-run 04, 05, 06</t>
         </is>
       </c>
-      <c r="F120" s="8" t="n"/>
-    </row>
-    <row r="121" ht="28" customHeight="1">
-      <c r="B121" s="12" t="inlineStr">
+      <c r="F128" s="8" t="n"/>
+    </row>
+    <row r="129" ht="43" customHeight="1">
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>SupplierNotInDimSupplier or ItemNotInDimItem is not 0</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>sql/04 built the dimension from differently trimmed or filtered values than the join in sql/05 uses</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>Make sql/04 trim and default the key exactly as sql/05 does (LTRIM(RTRIM()), 'Unknown Supplier'); re-run 04, 05, 06</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="B130" s="12" t="inlineStr">
         <is>
           <t>LoadedRows is larger</t>
         </is>
       </c>
-      <c r="C121" s="12" t="inlineStr">
+      <c r="C130" s="12" t="inlineStr">
         <is>
           <t>The fact was loaded twice without being emptied</t>
         </is>
       </c>
-      <c r="D121" s="8" t="n"/>
-      <c r="E121" s="12" t="inlineStr">
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="12" t="inlineStr">
         <is>
           <t>Re-run sql/05 — its procedure empties the table before loading</t>
         </is>
       </c>
-      <c r="F121" s="8" t="n"/>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="B122" s="13" t="inlineStr">
+      <c r="F130" s="8" t="n"/>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="B131" s="13" t="inlineStr">
         <is>
           <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="29" customHeight="1">
-      <c r="A123" s="16" t="n">
+    <row r="132" ht="29" customHeight="1">
+      <c r="A132" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B123" s="14" t="inlineStr">
+      <c r="B132" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 1. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="16" t="n">
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B124" s="14" t="inlineStr">
+      <c r="B133" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="B125" s="17" t="inlineStr">
+    <row r="134" ht="16" customHeight="1">
+      <c r="B134" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C125" s="14" t="inlineStr">
+      <c r="C134" s="14" t="inlineStr">
         <is>
           <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="B126" s="17" t="inlineStr">
+    <row r="135" ht="16" customHeight="1">
+      <c r="B135" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C126" s="14" t="inlineStr">
+      <c r="C135" s="14" t="inlineStr">
         <is>
           <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="B127" s="17" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="B136" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C127" s="14" t="inlineStr">
+      <c r="C136" s="14" t="inlineStr">
         <is>
           <t>What was observed: the same numbers.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="B128" s="17" t="inlineStr">
+    <row r="137" ht="16" customHeight="1">
+      <c r="B137" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C128" s="14" t="inlineStr">
+      <c r="C137" s="14" t="inlineStr">
         <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="16" t="n">
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B129" s="14" t="inlineStr">
+      <c r="B138" s="14" t="inlineStr">
         <is>
           <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="29" customHeight="1">
-      <c r="A130" s="16" t="n">
+    <row r="139" ht="29" customHeight="1">
+      <c r="A139" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B130" s="14" t="inlineStr">
+      <c r="B139" s="14" t="inlineStr">
         <is>
           <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="16" t="n">
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B131" s="14" t="inlineStr">
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="141" ht="8" customHeight="1"/>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="15" t="inlineStr">
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B134" s="14" t="inlineStr">
+      <c r="B143" s="14" t="inlineStr">
         <is>
           <t>At the model pass (gate G5), on the finished model.</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="15" t="inlineStr">
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B135" s="14" t="inlineStr">
+      <c r="B144" s="14" t="inlineStr">
         <is>
           <t>After every reload of the county data. Re-run sql/06 first, then this check.</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="15" t="inlineStr">
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B136" s="14" t="inlineStr">
+      <c r="B145" s="14" t="inlineStr">
         <is>
           <t>After any change to scripts sql/04 or sql/05.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="146" ht="8" customHeight="1"/>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="15" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B140" s="14" t="inlineStr">
+      <c r="B149" s="14" t="inlineStr">
         <is>
           <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="15" t="inlineStr">
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B141" s="14" t="inlineStr">
+      <c r="B150" s="14" t="inlineStr">
         <is>
           <t>Document 25 — when each check is run, and when to re-run it.</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="15" t="inlineStr">
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B142" s="14" t="inlineStr">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="B143" s="21" t="inlineStr">
+    <row r="152" ht="18" customHeight="1">
+      <c r="B152" s="21" t="inlineStr">
         <is>
           <t>Connect with SQL Server Management Studio</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="8" customHeight="1"/>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="153" ht="8" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="29" customHeight="1">
-      <c r="B146" s="14" t="inlineStr">
+    <row r="155" ht="29" customHeight="1">
+      <c r="B155" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="43.5" customHeight="1">
-      <c r="B147" s="14" t="inlineStr">
+    <row r="156" ht="43.5" customHeight="1">
+      <c r="B156" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="144">
-    <mergeCell ref="B129:F129"/>
+  <mergeCells count="154">
+    <mergeCell ref="B106:F106"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="A133:F133"/>
-    <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C89:D89"/>
     <mergeCell ref="B71:F71"/>
-    <mergeCell ref="C125:F125"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
+    <mergeCell ref="A86:F86"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="C136:F136"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="E128:F128"/>
     <mergeCell ref="B60:F60"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C107:F107"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="C121:F121"/>
+    <mergeCell ref="C134:F134"/>
+    <mergeCell ref="B84:F84"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C93:F93"/>
     <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="B133:F133"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="C105:F105"/>
     <mergeCell ref="C43:F43"/>
-    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="C120:F120"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="B135:F135"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="B54:F54"/>
+    <mergeCell ref="C135:F135"/>
     <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="B96:F96"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="C111:F111"/>
+    <mergeCell ref="B105:F105"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C92:F92"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="B107:F107"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B148:F148"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="C137:F137"/>
+    <mergeCell ref="B74:F74"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="C110:F110"/>
     <mergeCell ref="B75:F75"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="C119:F119"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B62:F62"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="C91:F91"/>
-    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="E130:F130"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="B46:F46"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="C128:D128"/>
     <mergeCell ref="C102:F102"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="B145:F145"/>
+    <mergeCell ref="C108:F108"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C129:D129"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="C45:F45"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="C128:F128"/>
+    <mergeCell ref="B87:F87"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="B147:F147"/>
     <mergeCell ref="C113:F113"/>
-    <mergeCell ref="E80:F80"/>
     <mergeCell ref="C29:F29"/>
+    <mergeCell ref="E89:F89"/>
     <mergeCell ref="C100:F100"/>
     <mergeCell ref="C112:F112"/>
-    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="C109:F109"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B65:F65"/>
-    <mergeCell ref="C127:F127"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C114:F114"/>
+    <mergeCell ref="E125:F125"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="E81:F81"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="A78:F78"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="B138:F138"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C106:F106"/>
+    <mergeCell ref="B156:F156"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="B140:F140"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="B130:F130"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B117:F117"/>
     <mergeCell ref="C101:F101"/>
-    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="B151:F151"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C104:F104"/>
+    <mergeCell ref="B132:F132"/>
     <mergeCell ref="C42:F42"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="A147:F147"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B103:F103"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C99:F99"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="C99:F99"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A123:F123"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="A138:F138"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="B79:F79"/>
